--- a/backend/data/financials_by_company/1PI.MI.xlsx
+++ b/backend/data/financials_by_company/1PI.MI.xlsx
@@ -4355,10 +4355,8 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>98109</t>
-        </is>
+      <c r="E2" t="n">
+        <v>98109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4657,7 +4655,7 @@
         <v>73869000</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ2" t="n">
         <v>0.52474</v>
